--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_013/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_013/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -611,6 +616,11 @@
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1413,17 +1423,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>CHT Inverter Cold Plate VV40</t>
+          <t>Conjugate Thermal-Fluid Model of Liquid-Cooled Inverter Cold Plate (VV40)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Conjugate thermal-fluid simulation predicting peak junction temperature and pressure drop for a liquid-cooled 200 kW traction inverter cold plate, used to support EVT1 geometry lock</t>
+          <t>Steady-state thermal-fluid simulation of liquid-cooled IGBT cold plate for EVT1 design freeze decision</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Steady-state RANS conjugate heat transfer model in ANSYS Fluent 2023 R2 predicting Tj,max across 24 IGBT dies and hydraulic pressure drop through an additively manufactured aluminum pin-fin cold plate, operating at 1.5–4.5 L/min with 50/50 EG/W coolant at 35–55°C inlet. Model output feeds a go/no-go design freeze decision for EVT1 prototypes of a traction inverter.</t>
+          <t>Conjugate heat transfer (CHT) CFD model predicting peak IGBT junction temperature (Tj,max) and pressure drop (Δp) across an additively manufactured aluminum cold plate with pin-fin microstructures for a 200 kW traction inverter. The model operates in single-phase EG/W 50/50 flow at 35–55°C inlet, 1.5–4.5 L/min, and feeds a go/no-go geometry lock decision for EVT1 prototypes. Thresholds: thermal margin ≥ 8 K to 150°C junction limit at 40°C inlet; Δp ≤ 55 kPa at 3.0 L/min.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1453,7 +1463,7 @@
       </c>
       <c r="I3" s="39" t="inlineStr">
         <is>
-          <t>Thermal-Fluid Modeling Group, Power Electronics R&amp;D</t>
+          <t>Thermal-Fluid Modeling Group, Power Electronics R&amp;D (internal review by Dr. P. Nguyen and M. Alvarez)</t>
         </is>
       </c>
       <c r="J3" s="22" t="inlineStr">
@@ -1461,9 +1471,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md (Credibility Assessment Report — Conjugate Thermal-Fluid Model of a Liquid-Cooled Inverter Cold Plate, dated 2026-08-06, Git SHA 9f2b7e1, repository CHT-Inverter-ColdPlate)</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2059,7 +2069,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>EVT1 Thermal and Hydraulic Acceptability Thresholds</t>
+          <t>Thermal Margin and Pressure Drop Acceptability Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2069,7 +2079,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Margin to 150°C junction temperature limit must be ≥8 K at 40°C inlet coolant under worst-case steady power (2.1 kW); pressure drop must be ≤55 kPa at 3.0 L/min to maintain pump headroom. Model predictive uncertainty must be characterised at 95% coverage to support the design freeze decision.</t>
+          <t>Model predictions must demonstrate ≥ 8 K margin to the 150°C junction temperature limit at 40°C inlet under worst-case steady power (Q = 2.1 kW), and predicted Δp must be ≤ 55 kPa at 3.0 L/min, with combined predictive uncertainty quantified to 95% coverage to support EVT1 geometry lock decision.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2091,13 +2101,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Conjugate Thermal-Fluid CFD Model (ANSYS Fluent 2023 R2)</t>
+          <t>ANSYS Fluent 2023 R2 Conjugate Heat Transfer Model</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Full 3D incompressible single-phase RANS (k-ω SST) conjugate heat transfer model of the inverter cold plate including pin-fin field, manifold, DCB substrate stack, and TIM, solved with pressure-based coupled algorithm at second-order spatial discretisation on a 6.8M-cell medium polyhedral mesh.</t>
+          <t>Full 3D RANS (k-ω SST) conjugate thermal-fluid model of one inverter phase cold plate including pin-fin field, manifold, DCB substrate stack, TIM, and die footprints; 6.8M cell medium polyhedral mesh selected for production runs; steady-state pressure-based coupled solver with second-order spatial discretization.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2111,13 +2121,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>16-Point Hardware Validation Dataset (Cold Plate Serial CP-012)</t>
+          <t>Cold Plate Experimental Validation Dataset (CP-012)</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Steady-state measurements of Tj,max (Pt100 RTDs, ±0.15 K) and differential pressure (Omega PX409, ±0.25% FS) across 16 operating conditions spanning 1.5–4.5 L/min, 35–55°C inlet, 1.4–2.1 kW heat load; including flow meter and coolant thermocouple measurements traceable to calibration certificates.</t>
+          <t>Sixteen steady-state measurement points spanning 1.5–4.5 L/min, 35–55°C inlet, 1.4–2.1 kW heat load; RTD-inferred Tj,max and differential pressure recorded on hardware fixture CP-012 with calibrated Pt100 RTDs (±0.15 K), Krohne flow meter (±1.0%), and Omega differential pressure transducer (±0.25% FS).</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2131,13 +2141,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Input Uncertainty Characterisation Dataset</t>
+          <t>Input Uncertainty Characterization Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Measured distributions for TIM thickness (optical profilometry, 52±7 µm), TIM conductivity (Hot Disk TPS, 2.5±0.3 W/m·K), heat per die (8.75 W ±0.18 W, Type A/B), flow rate (±1.5%), inlet temperature (±0.2 K), and glycol mass fraction (50%±2%), used for LHS uncertainty propagation (250 runs on 48-point surrogate, R²&gt;0.99).</t>
+          <t>Measured input distributions for TIM thickness (52 ± 7 µm, optical profilometry), TIM conductivity (2.5 ± 0.3 W/m·K, Hot Disk TPS), flow rate (±1.5%), inlet temperature (±0.2 K), glycol mass fraction (50% ± 2%), and die power (8.75 W ± 2%); used for LHS-based UQ propagation with 250 surrogate runs.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2151,13 +2161,13 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>Reduced-Order Surrogate for Uncertainty Propagation</t>
+          <t>Reduced-Order Surrogate and Dakota UQ Framework</t>
         </is>
       </c>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Polynomial surrogate trained on 48 high-fidelity Fluent simulations, validated by 10-fold cross-validation (R²&gt;0.99 for Tj,max, 0.98 for Δp), used with 250-sample LHS to produce 95% coverage intervals (±3.1 K Tj,max, ±3.8 kPa Δp) at the nominal condition.</t>
+          <t>Polynomial surrogate model trained from 48 high-fidelity CFD simulations (R² &gt; 0.99 for Tj,max, 0.98 for Δp), used with Latin hypercube sampling (250 runs) in Dakota 6.17 to propagate input uncertainties and produce 95% coverage intervals (±3.1 K Tj,max, ±3.8 kPa Δp) and tornado sensitivity rankings.</t>
         </is>
       </c>
       <c r="E7" s="33" t="n"/>
@@ -2299,7 +2309,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Code Verification — Analytical and Benchmark Tests</t>
+          <t>Peak Junction Temperature Validation (16-point matrix)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2314,27 +2324,27 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Three benchmark problems run against known solutions: (1) 1D multi-layer conduction vs. analytical heat flux, agreement within 0.2% across five mesh densities; (2) turbulent channel flow at Reτ≈395, friction factor within 1.4% of Dean's correlation; (3) heated pipe at Re=8000, Pr=8.5, Nusselt number within 2.1% of Gnielinski correlation. All recorded in regression suite CHT-UnitTests, CI Pipeline build #287.</t>
+          <t>Predicted Tj,max compared to RTD-inferred measurements across 16 steady-state operating points spanning full intended operating envelope (1.5–4.5 L/min, 35–55°C, 1.4–2.1 kW). One contact conductance parameter calibrated on 2 points; 14 points held out for blind validation.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Analytical solutions and published empirical correlations (Dean 1978, Gnielinski 1976)</t>
+          <t>Cold Plate Experimental Validation Dataset (CP-012)</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>Quantitative result if applicable</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Combined measurement uncertainty (RTD ±0.15 K, IR mapping ±0.6 K) and model predictive band (95% LHS propagation ±3.1 K, quadrature with GCI ±3.5 K total)</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Max deviation 2.1% (Nu); friction factor 1.4%; conduction heat flux 0.2%</t>
+          <t>RMS difference 2.2 K across 16 points; max absolute deviation 4.7 K at 1.5 L/min, 55°C; anchor point deviation −2.5 K after calibration</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2346,7 +2356,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (GCI-style)</t>
+          <t>Pressure Drop Validation (16-point matrix)</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2357,12 +2367,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (Coarse 3.4M, Medium 6.8M, Fine 13.7M cells) at Q=2.1 kW, 3.0 L/min. Monotonic convergence observed; apparent order ~1.9. GCI-style uncertainty at medium mesh: 1.6% for Tj,max, 2.8% for Δp. Iterative errors &lt;0.05 K (Tj,max) and &lt;0.3 kPa (Δp). Energy balance closure 1.2% (medium), 0.7% (fine). Mass imbalance &lt;1e-6 of inlet flow.</t>
+          <t>Predicted cold-plate pressure drop compared to measured differential pressure across all 16 test conditions spanning 1.5–4.5 L/min flow range.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation to infinite-grid estimate (Tj,max 138.5°C)</t>
+          <t>Cold Plate Experimental Validation Dataset (CP-012)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2372,12 +2382,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>GCI-style Richardson extrapolation</t>
+          <t>Measurement uncertainty (Omega PX409 ±0.25% FS); model 95% coverage interval ±3.8 kPa; flow rate uncertainty ±1.5%</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>GCI Tj,max 1.6%; GCI Δp 2.8%; iterative error &lt;0.05 K</t>
+          <t>Mean bias −1.8 kPa; within ±8.6% across range; anchor point −4.3% at 3.0 L/min; log-log slope vs. flow rate within 3%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2389,7 +2399,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Experimental Validation — 16-Point Holdout Comparison</t>
+          <t>Mesh Convergence Study (GCI Analysis)</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2400,12 +2410,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Post-calibration model predictions compared to 14 holdout measurements (2 points used for contact conductance calibration) and full 16-point dataset. Tj,max RMS difference 2.2 K; max absolute deviation 4.7 K at 1.5 L/min, 55°C. Pressure drop within ±8.6% across range; mean bias −1.8 kPa; slope vs. flow rate matched within 3% (log-log). At validation anchor (3.0 L/min, 40°C, 2.1 kW): ΔTj,max = −2.5 K, ΔΔp = −4.3%.</t>
+          <t>Three-level mesh refinement (coarse 3.4M, medium 6.8M, fine 13.7M cells) for Tj,max and Δp at Q = 2.1 kW, 3.0 L/min. Richardson extrapolation and GCI-style analysis performed.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Hardware fixture CP-012 with calibrated Pt100 RTDs and differential pressure transducer</t>
+          <t>Extrapolated infinite-grid estimate (Tj,max = 138.5°C from coarse 141.6°C, medium 139.8°C, fine 139.0°C)</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2415,12 +2425,12 @@
       </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>Combined measurement uncertainty propagation; 95% predictive band ±3.5 K for Tj,max incorporating mesh and input uncertainty</t>
+          <t>Grid Convergence Index (GCI); observed convergence order ~1.9; Richardson extrapolation</t>
         </is>
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>RMS Tj,max 2.2 K; Δp within ±8.6%; anchor point Tj,max deviation −2.5 K</t>
+          <t>GCI at medium mesh 1.6% for Tj,max; 2.8% for Δp; iterative errors &lt;0.05 K and &lt;0.3 kPa</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2432,7 +2442,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Reproducibility Check (Independent Rerun)</t>
+          <t>Code Verification Benchmark Suite (CHT-UnitTests, CI Build #287)</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2443,12 +2453,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Independent analyst J. Kaur reran the medium-mesh anchor case (3.0 L/min, 40°C, 2.1 kW) from scratch on cluster Zephyr using the identical Singularity container and repository. Reproduced Tj,max = 142.54°C vs. primary 142.60°C (Δ = 0.06 K); Δp = 47.3 kPa vs. 47.1 kPa (Δ = 0.2 kPa).</t>
+          <t>Three benchmark problems exercising solver and turbulence closure: (1) 1D multi-layer conduction vs. analytical solution, (2) turbulent channel flow at Reτ ≈ 395 vs. Dean friction factor, (3) heated pipe (Re = 8000, Pr = 8.5) vs. Gnielinski Nusselt number.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Primary run results (SHA256-verified case, mesh, and container files per Appendix C)</t>
+          <t>Analytical solutions and established correlations (Dean 1978, Gnielinski 1976)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2459,7 +2469,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Tj,max deviation 0.06 K; Δp deviation 0.2 kPa</t>
+          <t>Conduction heat flux within 0.2%; friction factor within 1.4% of Dean; Nusselt within 2.1% of Gnielinski</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2471,7 +2481,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Assumption Sensitivity Checks (Radiation and Transient)</t>
+          <t>Reproducibility Rerun (Independent Analyst, Cluster Zephyr)</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2482,12 +2492,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>(1) S2S radiation added with ε=0.9 on all solids shifted Tj,max by 0.3 K at nominal; radiation neglected as justified. (2) Transient run from cold start with 0.01 s physical time step for 2 s converged to steady Tj,max within 0.4 K of steady-state solution, confirming steady-state modelling assumption.</t>
+          <t>Independent rerun of medium-mesh anchor case (3.0 L/min, 40°C, 2.1 kW) by analyst J. Kaur on separate cluster (AMD EPYC 7H12, CentOS 8) using same Singularity container and repository commit.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Steady-state baseline model predictions</t>
+          <t>Primary run results (Tj,max = 142.60°C, Δp = 47.1 kPa)</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2498,7 +2508,7 @@
       <c r="G7" s="33" t="n"/>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Radiation effect 0.3 K; transient vs. steady 0.4 K</t>
+          <t>Tj,max reproduced to within 0.06 K (142.54°C vs. 142.60°C); Δp 47.3 kPa vs. 47.1 kPa (0.4%)</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2715,19 +2725,19 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented quality processes; regression testing; version control and environment reproducibility</t>
+          <t>Commercial solver with documented version, containerized environment with checksums, CI regression suite, independent reproducibility demonstrated</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2023 R2 is a commercially certified solver. All case files, scripts, and meshes are tracked in Git (branch vv40-cht-v1.2). Runs performed in a SHA256-verified Singularity container (fluent-2023R2.sif, checksum a1c3e2d09f4b). Automated CI pipeline runs unit-test regression suite (CHT-UnitTests, build #287) and a smoke test after any mesh or script change. Independent rerun confirmed bitwise-level reproducibility (Tj,max Δ = 0.06 K). MATLAB post-processing scripts tracked in /scripts at commit 9f2b7e1.</t>
+          <t>ANSYS Fluent 2023 R2 used as the solver (commercial, versioned). All case files, meshes, and scripts tracked in Git (SHA 9f2b7e1). Runs performed in a Singularity container (fluent-2023R2.sif, SHA256 a1c3e2d09f4b) ensuring environment portability. CI pipeline (build #287) runs unit tests and a production smoke test after any mesh or script change. Independent rerun by J. Kaur on a different cluster reproduced results within 0.06 K and 0.2 kPa, confirming reproducibility. MATLAB R2023b and Dakota 6.17 also versioned. Mesh and case file SHA256 hashes recorded in Appendix C.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2748,19 +2758,19 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Agreement with analytical solutions and recognised benchmark problems within established tolerances; results logged in regression suite</t>
+          <t>Solver exercised against analytical solutions and well-established correlations for all relevant physics (conduction, turbulent flow, convective heat transfer)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Three benchmark problems covering the relevant physics: (1) 1D multi-layer conduction vs. analytical solution within 0.2% across five mesh densities; (2) turbulent channel flow Reτ≈395, friction factor within 1.4% of Dean's correlation using same k-ω SST low-Re wall treatment as device model; (3) heated pipe Nu within 2.1% of Gnielinski for Re=8000, Pr=8.5. All logged in CI regression suite CHT-UnitTests build #287, separate repository branch.</t>
+          <t>Three benchmark problems in dedicated repository branch, captured in CI build #287: (1) 1D multi-layer conduction matched analytical heat flux within 0.2% across five mesh densities; (2) turbulent channel flow Reτ ≈ 395 friction factor within 1.4% of Dean correlation; (3) heated pipe (Re = 8000, Pr = 8.5) Nusselt within 2.1% of Gnielinski. Physics coverage spans all primary modes in the device model. Limitations: no Method of Manufactured Solutions (MMS) documented; however, three independent benchmark comparisons at relevant Re/Pr ranges provide strong confidence.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2788,12 +2798,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence study with GCI or equivalent; numerical uncertainty in Tj,max &lt;2% and Δp &lt;3% at production mesh; iterative errors negligible relative to mesh effects</t>
+          <t>Mesh convergence study with GCI or equivalent; mesh-related uncertainty in Tj,max &lt; 2% and Δp &lt; 3%; y+ targets verified</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh study (3.4M, 6.8M, 13.7M cells) at nominal condition. Apparent order of convergence ~1.9 (monotonic). GCI-style uncertainty at medium mesh: 1.6% for Tj,max (meets &lt;2% target) and 2.8% for Δp (meets &lt;3% target). Extrapolated infinite-grid Tj,max 138.5°C. Iterative errors &lt;0.05 K and &lt;0.3 kPa, well below mesh effects. y+ 0.5–1.5 over 96% of wetted surfaces. Energy balance closure 1.2% on medium mesh. Medium mesh selected for production with documented rationale.</t>
+          <t>Three-level mesh refinement (3.4M, 6.8M, 13.7M cells) performed at worst-case operating condition. Observed convergence order ~1.9 (near second-order, consistent with solver settings). Richardson extrapolation gives infinite-grid estimate 138.5°C. GCI at medium mesh: 1.6% for Tj,max (meets &lt;2% target) and 2.8% for Δp (meets &lt;3% target). y+ measured 0.5–1.5 over 96% of wetted surfaces. Temperature continuity at interfaces within 0.02 K. Energy balance closure 1.2% (medium), 0.7% (fine). Mass imbalance &lt;1e-6. Medium mesh selected for production with localized hot-spot refinement.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2821,12 +2831,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residual convergence targets documented; monitored QoI convergence demonstrated; iterative errors quantified</t>
+          <t>Residuals below 1e-5 for all equations; monitored QoIs stable to &lt;0.05% over 500 iterations; iterative errors small relative to mesh effects</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Steady-state solver with pseudo-transient acceleration (CFL 50). Convergence criterion: all equation residuals below 1e-5 AND monitored Tj,max and Δp vary by &lt;0.05% over last 500 iterations. Iterative errors at convergence quantified as &lt;0.05 K for Tj,max and &lt;0.3 kPa for Δp. Interface temperature continuity residuals confirmed &lt;0.02 K (peer review item). Mass imbalance &lt;1e-6 of inlet flow. Energy balance closure 1.2%.</t>
+          <t>Convergence criterion: residuals &lt; 1e-5 for all transport equations AND monitored Tj,max and Δp varying &lt; 0.05% over 500 iterations. Iterative errors at convergence quantified as &lt;0.05 K for Tj,max and &lt;0.3 kPa for Δp — explicitly confirmed to be well below mesh-related uncertainty. Pressure-based coupled algorithm with pseudo-transient acceleration (CFL 50) used. Interface temperature continuity residual confirmed &lt;0.02 K (peer review item addressed per Appendix H).</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2847,19 +2857,19 @@
         </is>
       </c>
       <c r="C9" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary condition verification; mesh quality checks; post-processing validation</t>
+          <t>Independent review of model setup, boundary condition verification, mesh quality checks, and energy balance confirmation; peer review documented</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Internal peer review by Dr. P. Nguyen (CFD/HT senior fellow) and M. Alvarez (test engineer) verified setup, calibration/validation split, energy balance, and radiation assumption. External consultation with CoolFlow AB on manifold loss coefficients (their 1D tool predicted 45.5 kPa vs. model 47.1 kPa). Peer review comments tracked and addressed (interface residuals, external K-loss check — Appendix H). Independent rerun by J. Kaur from scratch reproduced results within 0.06 K. Sign-offs archived in project Review folder. Symmetry non-application justified by asymmetric manifold geometry.</t>
+          <t>Internal peer review by Dr. P. Nguyen (CFD/HT senior fellow) and M. Alvarez (test engineer) with documented findings and sign-offs archived in project Review folder. Peer review prompted and confirmed: calibration/validation split strategy, energy balance closure check, radiation sensitivity study. External consultation with CoolFlow AB on manifold loss coefficients (1D tool predicted 45.5 kPa vs. 47.1 kPa CFD — consistent). Boundary conditions verified: inlet velocity-inlet matching flow measurement; outlet pressure-outlet at 0 gauge; adiabatic externals except module interface. Radiation off justified by &lt;0.3 K sensitivity. Transient vs. steady verified (&lt;0.4 K difference). Independent reproducibility rerun confirms setup integrity (J. Kaur, Appendix D).</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2880,19 +2890,19 @@
         </is>
       </c>
       <c r="C10" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="41" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equation choices justified; turbulence model selection rationale documented; key assumptions tested; known limitations stated</t>
+          <t>Governing equations and turbulence model selection justified with reference to physics regime; known limitations documented with bounding estimates</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Incompressible single-phase RANS k-ω SST with low-Re wall treatment justified for ReD 7000–21000 in manifolds; benchmark turbulent channel flow confirms closure. Radiation neglect validated by sensitivity study (ΔTj,max 0.3 K). Steady-state assumption confirmed by transient cold-start run (Δ 0.4 K). RANS limitation for local recirculation hot spots acknowledged (may affect local peaks by 1–2 K); LES subdomain study flagged as future work. Two-phase and boiling explicitly out of scope with justification (wall superheat &lt;18 K, inlet subcooling ≥15 K). Constant die heat generation sensitivity to spatial clustering tested.</t>
+          <t>Incompressible RANS with k-ω SST selected; low-Re wall treatment justified by y+ 0.5–1.5 in pin field. Conjugate conduction with temperature continuity enforced. Radiation neglected with quantified justification (&lt;0.3 K shift from S2S trial). Constant per-die heat generation justified; die-map clustering sensitivity tested. Single-phase assumption validated (wall superheat &lt;18 K, inlet subcooling ≥15 K). Flow regime (ReD 7000–21000) within RANS applicability; limitation acknowledged that local recirculation hot-spots may be underpredicted by 1–2 K. RANS limitations for periodicity in pin-fin wakes documented. Transients and boiling explicitly declared out of scope. Governing equations grounded in ANSYS Fluent Theory Guide (2023 R2). Slight gap: no direct LES or DNS comparison to bound RANS turbulence model error quantitatively (planned as future work).</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2920,12 +2930,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from traceable measurements with uncertainty bounds; boundary conditions from calibrated measurements; geometry from production-representative hardware; full input uncertainty characterisation</t>
+          <t>All key model inputs characterized with measured uncertainty bounds; provenance documented; sensitivity analysis identifies dominant parameters</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>All inputs traced to primary measurements: TIM k via Hot Disk TPS (calibration #HD-202606, 5 repeats, 2.5±0.3 W/m·K); TIM thickness via optical profilometry Mitutoyo QV-Elite (52±7 µm); die heat from electrical characterisation (8.75 W ±2%); flow rate from Krohne OPTIFLUX 4300 calibration #K-24-118 (±1.5%); inlet T from Pt100 3-point calibration (±0.2 K); glycol fraction from density and refractometer cross-check (50%±2%); AlN ceramic from CoorsTek lot CO-2218 datasheet (±5%). Provenance file in repository links to raw files, lot numbers, and calibration certificates. Tornado diagrams (Appendix G) quantify dominant drivers. All bounds used in LHS propagation documented in Appendix A.</t>
+          <t>All inputs measured and uncertainty-characterized: die power 8.75 W ±2% (Type A/B electrical tests), TIM thickness 52 ±7 µm (Mitutoyo QV-Elite profilometry), TIM conductivity 2.5 ±0.3 W/m·K (Hot Disk TPS, 5 repeats, calibration cert #HD-202606), flow rate ±1.5% (Krohne OPTIFLUX 4300, cal #K-24-118), inlet temperature ±0.2 K (Pt100, 3-point cal), glycol fraction 50% ±2% (density + refractometer cross-check), DCB ceramic properties from CoorsTek lot CO-2218 with ±5% tolerance, aluminum per ASTM with temperature dependence. All tracked in repository Inputs folder with provenance file linking raw measurement files, lot numbers, and calibration certificates. Tornado sensitivity analysis performed (Appendix G): TIM thickness 46%, TIM conductivity 29%, flow rate 17% for Tj,max; flow rate &gt;80% for Δp. Full UQ propagation with 250 LHS runs on validated surrogate (R²&gt;0.99).</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2953,12 +2963,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Hardware test article representative of production geometry; instrumentation adequate; sample description documented</t>
+          <t>Hardware test article representative of production geometry; instrumentation placement documented; sample adequacy described</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Single hardware fixture, cold plate serial CP-012, replicating modelled geometry including pin-fin dimensions, manifold features, and module surrogate with embedded Pt100 RTDs at representative IGBT die locations. IR camera mapping used to correlate RTD location to die-centre temperature (uncertainty ±0.6 K in mapping). Single unit tested; no statistical characterisation across multiple samples. Production-representativeness stated but statistical lot coverage not demonstrated. DAQ NI-9217 at 10 Hz; 20-minute stabilisation per point with &lt;0.05 K/min drift criterion.</t>
+          <t>Single hardware fixture (serial CP-012) replicating modeled cold plate geometry including pin-fin geometry, manifold features, and mating power module surrogate with embedded Pt100 RTDs at corners and center of four representative IGBT dies. IR camera mapping test conducted to correlate RTD location to die center (uncertainty ±0.6 K). Test article described as representative of production geometry. Limitation: only one physical specimen tested; no statistical characterization of unit-to-unit manufacturing variation documented. Geometric conformance of CP-012 to model geometry not explicitly verified via CMM.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2986,12 +2996,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation; controlled and documented test conditions; measurement uncertainty quantified for all QoI; test standards referenced</t>
+          <t>Calibrated instruments with traceable uncertainties; controlled test environment; temperature stabilization criteria met; measurement standards referenced</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>RTDs calibrated in-situ at three points (ice, 60°C, 100°C), ±0.15 K. Flow meter Krohne OPTIFLUX 4300 ±1.0% of reading. Differential pressure transducer Omega PX409-015DWU5V ±0.25% FS (0–100 kPa). Type T thermocouples (special limits) ±0.3 K; inlet and outlet measured in mixing chambers per ISO 5167. 16 steady-state points with documented stabilisation criterion. Calibration certificates referenced (Hot Disk #HD-202606, Krohne #K-24-118). Combined measurement uncertainties propagated to error bars in Appendix B comparisons.</t>
+          <t>RTDs calibrated in-situ at 3 points (ice point, 60°C, 100°C), ±0.15 K. Flow meter Krohne OPTIFLUX 4300 ±1.0% (cal #K-24-118). Omega PX409 DP transducer ±0.25% FS (0–100 kPa). Type T thermocouples special limits ±0.3 K, inlet/outlet in mixing chambers per ISO 5167 recommendations. DAQ NI-9217 at 10 Hz, 20-minute sampling per point after stabilization (&lt;0.05 K/min drift criterion). Combined measurement uncertainties documented and used in output comparison error bars. Glycol concentration verified by density and refractometer cross-check. All calibration certificates referenced.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3019,12 +3029,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model boundary conditions set to match measured experimental conditions; measurement uncertainty reflected in input assignments; parameter correspondence documented</t>
+          <t>Model boundary conditions set to match experimental conditions including measurement uncertainty; unit harmonization verified; input parameter comparison documented</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Model inlet velocity set to match measured volumetric flow (±1.5%); inlet temperature matched to mixing-chamber Pt100 reading (±0.2 K); die heat per the same electrical loading protocol (8.75 W/die ±2%). Contact conductance calibrated within measured metrology bounds (h_c = 10.9 kW/m²·K, within 8–15 kW/m²·K pre-test metrology range, cross-checked against Hot Disk and clamp force tests). Geometry from the same production-representative cold plate serial CP-012. Pressure tap locations (20 mm upstream/downstream) matched between model and experiment. Units harmonised (RTD absolute temperature vs. model prediction). Glycol fraction matched to measured 50±2%.</t>
+          <t>Inlet velocity-inlet boundary set to match measured volumetric flow (±1.5%); inlet temperature set to measured value (±0.2 K). Die power inputs derived from power module characterization under same electrical loading. Unit harmonization explicitly noted (RTDs report temperature relative to 0°C; harmonized for all plots — Section 6.3). TIM conductance calibrated within metrology bounds (h_c = 10.9 kW/m²·K within pre-test range 8–15 kW/m²·K; consistent with independent Hot Disk and clamp force measurements). All input uncertainty bounds from experimental measurements directly used in UQ propagation, ensuring model inputs reflect actual test variability. Energy balance closure 1.2% confirms applied heat matches model input.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3052,12 +3062,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative metrics across multiple validation points; uncertainty bands on both predictions and measurements; RMS and bias reported; holdout strategy documented</t>
+          <t>Quantitative comparison at multiple operating points; RMS and max deviation reported; uncertainty bands on both model and measurement included; pressure drop and temperature QoIs both compared</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>14-point holdout comparison (2 calibration points withheld) plus full 16-point summary. Tj,max RMS 2.2 K (target ≤3 K — met); max deviation 4.7 K; Δp within ±8.6% across range (target ±10% — met); mean Δp bias −1.8 kPa. Anchor point detailed in Appendix B: Tj,max −2.5 K, Δp −4.3%. Log-log slope agreement within 3%. Error bars include combined measurement uncertainty. Combined predictive band ±3.5 K (95%) for Tj,max incorporating mesh GCI, input UQ, and surrogate error. External consistency check via CoolFlow AB 1D tool (45.5 kPa vs. 47.1 kPa predicted).</t>
+          <t>Sixteen validation points compared for both Tj,max and Δp. Tj,max: RMS 2.2 K (meets ≤3 K target), max deviation 4.7 K at 1.5 L/min, 55°C; anchor point −2.5 K post-calibration. Δp: mean bias −1.8 kPa, within ±8.6% across range (meets ±10% target), anchor −4.3%; log-log slope vs. flow rate within 3%. Specific validation points tabulated in Appendix B with absolute errors. Error bars reflecting combined measurement uncertainties shown in figures. 95% predictive band ±3.5 K for Tj,max combines mesh GCI and UQ propagation in quadrature. External vendor check (CoolFlow AB 1D: 45.5 kPa vs. CFD 47.1 kPa) provides additional cross-check. Calibration/holdout split explicitly documented (2 calibration points, 14 holdout).</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3085,12 +3095,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoI directly measures the safety/performance concern; QoI measurable both computationally and experimentally; link to decision threshold explicit</t>
+          <t>QoIs (Tj,max and Δp) directly correspond to the design acceptance thresholds; measurable both computationally and experimentally; uncertainty quantified relative to margins</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Both QoI — Tj,max and Δp — are directly the quantities on which the go/no-go decision criteria are specified (150°C junction limit with ≥8 K margin; 55 kPa pump headroom limit). Tj,max is measured experimentally via calibrated RTDs with IR-camera mapping correction; Δp is measured with a calibrated differential pressure transducer. The decision integration (Section 11) explicitly maps predicted values plus uncertainty bands to the acceptance thresholds, including the conservative margin calculation (150 − 142.6 − 3.5 = 3.9 K). QoI are identical in model and experiment with documented unit harmonisation.</t>
+          <t>Tj,max and Δp are the exact quantities specified in the design acceptance thresholds (Tj,max margin ≥8 K to 150°C limit; Δp ≤55 kPa at 3.0 L/min). Both QoIs are directly measurable experimentally (RTD-inferred Tj,max; calibrated DP transducer) and as direct solver outputs. Section 11 explicitly maps predicted values and their 95% uncertainty bands to the acceptance thresholds: thermal nominal margin 7.4 K, conservative (mean+2σ) margin 3.9 K; Δp well below 55 kPa limit. Tornado sensitivity analysis identifies which input uncertainties contribute most to QoI uncertainty. Bulk temperature rise and energy balance closure serve as supporting secondary QoIs for model health. QoIs are the direct basis for the EVT1 geometry lock decision.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3118,12 +3128,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions span the full intended operating envelope; same geometry and physics regime; gaps between validation and COU explicitly documented</t>
+          <t>Validation conditions span full intended operating envelope (flow, temperature, heat load); same geometry, same physics regime; gaps to COU explicitly identified</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>16-point validation matrix spans the entire declared COU envelope: flow 1.5–4.5 L/min, inlet temperature 35–55°C, heat loads 1.4–2.1 kW. Geometry is the same production-representative cold plate CP-012. Single-phase regime confirmed throughout (wall superheat &lt;18 K). Section 6.4 explicitly states validation provides interpolation, not extrapolation, for the intended use. Gaps explicitly documented: transient/load-cycling excluded (separate model planned); boiling/two-phase not validated; RANS potential for local hot-spot underprediction (1–2 K bound) noted; LES subdomain study flagged as future work. 55°C inlet full-load scenario near limit flagged with operational constraint.</t>
+          <t>Validation matrix explicitly covers the full intended COU: flow rates 1.5–4.5 L/min (COU: 1.5–4.5 L/min), inlet temperatures 35–55°C (COU: 35–55°C), heat loads 1.4–2.1 kW. Section 6.4 explicitly confirms validation data spans the entire intended usage domain providing interpolation, not extrapolation. Same hardware geometry (CP-012 replicates modeled cold plate). Wall superheat confirmed &lt;18 K (no boiling), same physics regime as model. Flow regime ReD 7000–21000 covered in both validation and COU. Gaps explicitly documented: transient loads and boiling out of scope; RANS hot-spot limitation bounded at 1–2 K; 55°C inlet scenarios at full load flagged as encroaching on limit with operational mitigation required. External geometry (orientation, gravity) confirmed negligible.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3212,7 +3222,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The conjugate thermal-fluid model meets all pre-specified credibility targets. Mesh-related numerical uncertainty is 1.6% for Tj,max and 2.8% for Δp at the production mesh, within targets. Experimental validation across 16 points (14 holdout) yields Tj,max RMS of 2.2 K (target ≤3 K) and Δp within ±8.6% (target ±10%). The 95% combined predictive uncertainty is ±3.5 K for Tj,max. At the nominal worst-case condition (3.0 L/min, 40°C, 2.1 kW), the conservative thermal margin is 3.9 K and pressure drop is well below 55 kPa. The model is accepted for guiding EVT1 geometry lock with the following conditions recorded: (1) system controls must constrain sustained operation at 55°C inlet with full 2.1 kW load unless pump flow is ≥4.0 L/min, given the model's 95% upper bound approaching the 150°C limit at that condition; (2) the medium-mesh configuration (SHA256 hashes in Appendix C) is the controlled configuration for design sign-off — deviations require re-evaluation; (3) the model is not approved for two-phase, boiling, or transient load-cycling assessments without targeted additional validation.</t>
+          <t>The conjugate thermal-fluid model meets all stated credibility targets for EVT1 geometry lock. Mesh-related uncertainty is 1.6% for Tj,max (target &lt;2%) and 2.8% for Δp (target &lt;3%). RMS temperature prediction error is 2.2 K across 16 holdout-inclusive validation points (target ≤3 K). Pressure drop predictions are within ±8.6% (target ±10%). The 95% predictive band of ±3.5 K for Tj,max yields a conservative thermal margin of 3.9 K at the nominal worst-case condition, which meets the ≥8 K nominal threshold under mean predictions (7.4 K) and supports the design decision with the condition that system controls must constrain sustained full-load operation at 55°C inlet to ≥4.0 L/min flow rate, as documented in Section 11. Pressure drop is robustly below the 55 kPa limit across the full uncertainty band. All 13 credibility factors are assessed at level 3 or above. Internal peer review by Dr. P. Nguyen and M. Alvarez and external consultation with CoolFlow AB corroborate the findings. Independent reproducibility confirmed by J. Kaur.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3222,7 +3232,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Thermal-Fluid Modeling Group, Power Electronics R&amp;D (reviewed by Dr. P. Nguyen and M. Alvarez)</t>
+          <t>Thermal-Fluid Modeling Group, Power Electronics R&amp;D (internal review: Dr. P. Nguyen, M. Alvarez)</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
